--- a/artfynd/A 34881-2025 artfynd.xlsx
+++ b/artfynd/A 34881-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118227248</v>
+        <v>118227143</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559792</v>
+        <v>559642</v>
       </c>
       <c r="R2" t="n">
-        <v>7077593</v>
+        <v>7077753</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,42 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118227156</v>
+        <v>118227116</v>
       </c>
       <c r="B3" t="n">
-        <v>74596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559651</v>
+        <v>559626</v>
       </c>
       <c r="R3" t="n">
-        <v>7077762</v>
+        <v>7077889</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118227210</v>
+        <v>118227248</v>
       </c>
       <c r="B4" t="n">
-        <v>74596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559829</v>
+        <v>559792</v>
       </c>
       <c r="R4" t="n">
-        <v>7077655</v>
+        <v>7077593</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,43 +979,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118227191</v>
+        <v>118227156</v>
       </c>
       <c r="B5" t="n">
-        <v>97750</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559644</v>
+        <v>559651</v>
       </c>
       <c r="R5" t="n">
-        <v>7077805</v>
+        <v>7077762</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118227230</v>
+        <v>118227210</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559834</v>
+        <v>559829</v>
       </c>
       <c r="R6" t="n">
-        <v>7077567</v>
+        <v>7077655</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118227143</v>
+        <v>118227230</v>
       </c>
       <c r="B7" t="n">
-        <v>82263</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559642</v>
+        <v>559834</v>
       </c>
       <c r="R7" t="n">
-        <v>7077753</v>
+        <v>7077567</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1309,6 +1279,108 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118227191</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>kråkbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559644</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7077805</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34881-2025 artfynd.xlsx
+++ b/artfynd/A 34881-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118227143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118227116</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118227248</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118227156</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118227210</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118227230</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,8 +1416,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118227191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>